--- a/source/relatorios/2025/7-jul.xlsx
+++ b/source/relatorios/2025/7-jul.xlsx
@@ -896,9 +896,15 @@
       <c r="C34" s="2" t="n">
         <v>1000</v>
       </c>
-      <c r="D34" s="1"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="1"/>
+      <c r="D34" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="G34" s="1" t="n">
         <v>7</v>
       </c>

--- a/source/relatorios/2025/7-jul.xlsx
+++ b/source/relatorios/2025/7-jul.xlsx
@@ -896,15 +896,9 @@
       <c r="C34" s="2" t="n">
         <v>1000</v>
       </c>
-      <c r="D34" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="D34" s="1"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="1"/>
       <c r="G34" s="1" t="n">
         <v>7</v>
       </c>
